--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488227_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488227_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6402</v>
+        <v>1.9574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7294</v>
+        <v>1.5883</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.3691</v>
       </c>
       <c r="G2" t="n">
         <v>0.2288</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0578</v>
+        <v>0.3749</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3084</v>
+        <v>0.1673</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7493</v>
+        <v>0.2076</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3139</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4976</v>
+        <v>0.2005</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0051</v>
+        <v>0.496</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4925</v>
+        <v>-0.2956</v>
       </c>
       <c r="G5" t="n">
         <v>1.9641</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8536</v>
+        <v>-0.1554</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7909</v>
+        <v>-0.2897</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.1343</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1259</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1036</v>
+        <v>-1.0243</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0359</v>
+        <v>-0.9811</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0677</v>
+        <v>-0.0431</v>
       </c>
       <c r="G6" t="n">
         <v>0.177</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3542</v>
+        <v>-0.2748</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1094</v>
+        <v>-0.0547</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2447</v>
+        <v>-0.2201</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2488</v>
+        <v>-2.1684</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2333</v>
+        <v>-2.3745</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0155</v>
+        <v>0.2061</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7634</v>
@@ -1000,13 +1000,13 @@
         <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4118</v>
+        <v>-0.3314</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0497</v>
+        <v>-0.1909</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3621</v>
+        <v>-0.1405</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2863</v>
+        <v>-2.184</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4044</v>
+        <v>-2.0559</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1182</v>
+        <v>-0.128</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6311</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3581</v>
+        <v>-0.2559</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5471</v>
+        <v>-0.1986</v>
       </c>
       <c r="U8" t="n">
-        <v>0.189</v>
+        <v>-0.0572</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1744</v>
+        <v>-3.967</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9395</v>
+        <v>-2.7322</v>
       </c>
       <c r="F9" t="n">
         <v>-1.2349</v>
@@ -1156,10 +1156,10 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.48</v>
+        <v>-0.2726</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.286</v>
+        <v>-0.0786</v>
       </c>
       <c r="U9" t="n">
         <v>-0.194</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6771</v>
+        <v>-4.4892</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0669</v>
+        <v>-1.5303</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6102</v>
+        <v>-2.9589</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4223</v>
+        <v>0.0665</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.5834</v>
+        <v>-0.6262</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8389</v>
+        <v>0.6927</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0323</v>
+        <v>0.1098</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5466</v>
+        <v>0.047</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4857</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.39</v>
+        <v>-0.0433</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0368</v>
+        <v>-0.6731</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3531</v>
+        <v>0.6299</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>1.004</v>
+        <v>-0.1116</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8183</v>
+        <v>-0.1016</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1858</v>
+        <v>-0.01</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2589</v>
+        <v>-3.1471</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2589</v>
+        <v>-3.4616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.917</v>
+        <v>-5.5776</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9335</v>
+        <v>-3.8936</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9836</v>
+        <v>-1.684</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0665</v>
+        <v>-4.4223</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6262</v>
+        <v>-3.5834</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6927</v>
+        <v>-0.8389</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1098</v>
+        <v>-2.0323</v>
       </c>
       <c r="K11" t="n">
-        <v>0.047</v>
+        <v>-1.5466</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.4857</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0433</v>
+        <v>-2.39</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6731</v>
+        <v>-2.0368</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6299</v>
+        <v>-0.3531</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5394</v>
+        <v>0.1035</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5049</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0346</v>
+        <v>0.1119</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.1471</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.4616</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3234</v>
+        <v>-5.8989</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.055</v>
+        <v>-1.729</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2684</v>
+        <v>-4.17</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9412</v>
@@ -1390,13 +1390,13 @@
         <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7235</v>
+        <v>0.148</v>
       </c>
       <c r="T12" t="n">
-        <v>0.827</v>
+        <v>0.153</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1035</v>
+        <v>-0.005</v>
       </c>
       <c r="V12" t="n">
         <v>-3.588</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4144</v>
+        <v>-5.992</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.884</v>
+        <v>-4.5354</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5305</v>
+        <v>-1.4566</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7906</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3126</v>
+        <v>0.1097</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.572</v>
+        <v>-0.2235</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2594</v>
+        <v>0.3333</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3847</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.5283</v>
+        <v>-6.5665</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.3515</v>
+        <v>-5.6113</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1768</v>
+        <v>-0.9552</v>
       </c>
       <c r="G14" t="n">
         <v>-6.9753</v>
@@ -1546,13 +1546,13 @@
         <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2413</v>
+        <v>-0.2795</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0644</v>
+        <v>-0.3242</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1768</v>
+        <v>0.0448</v>
       </c>
       <c r="V14" t="n">
         <v>0.503</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.9645</v>
+        <v>-34.1438</v>
       </c>
       <c r="E15" t="n">
-        <v>-22.6135</v>
+        <v>-21.7928</v>
       </c>
       <c r="F15" t="n">
         <v>-12.3511</v>
@@ -1594,7 +1594,7 @@
         <v>-23.2848</v>
       </c>
       <c r="I15" t="n">
-        <v>4.492000000000001</v>
+        <v>4.491999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>-3.6681</v>
@@ -1624,10 +1624,10 @@
         <v>13.8964</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7657</v>
+        <v>-0.9450999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.9707</v>
+        <v>-1.1499</v>
       </c>
       <c r="U15" t="n">
         <v>0.2050999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.591799999999999</v>
+        <v>9.057399999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3936</v>
+        <v>4.0019</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1982</v>
+        <v>5.0555</v>
       </c>
       <c r="G16" t="n">
         <v>2.6271</v>
@@ -1702,13 +1702,13 @@
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5205</v>
+        <v>0.9861</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3631</v>
+        <v>-0.0286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1574</v>
+        <v>1.0147</v>
       </c>
       <c r="V16" t="n">
         <v>3.7766</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.7384</v>
+        <v>6.5843</v>
       </c>
       <c r="E17" t="n">
-        <v>5.84</v>
+        <v>5.2524</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8984</v>
+        <v>1.3319</v>
       </c>
       <c r="G17" t="n">
         <v>2.714</v>
@@ -1780,13 +1780,13 @@
         <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8772</v>
+        <v>0.7231</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0197</v>
+        <v>0.4321</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1425</v>
+        <v>0.291</v>
       </c>
       <c r="V17" t="n">
         <v>3.1471</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.0245</v>
+        <v>6.167</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8379</v>
+        <v>2.3275</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1866</v>
+        <v>3.8395</v>
       </c>
       <c r="G18" t="n">
         <v>3.7689</v>
@@ -1858,13 +1858,13 @@
         <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6703</v>
+        <v>0.4722</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.3646</v>
       </c>
       <c r="U18" t="n">
-        <v>0.184</v>
+        <v>0.8369</v>
       </c>
       <c r="V18" t="n">
         <v>0.6289</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.5819</v>
+        <v>5.3064</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0178</v>
+        <v>1.8012</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5641</v>
+        <v>3.5052</v>
       </c>
       <c r="G19" t="n">
         <v>1.8738</v>
@@ -1936,13 +1936,13 @@
         <v>2.594</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2184</v>
+        <v>0.5061</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5807</v>
+        <v>0.2027</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3623</v>
+        <v>0.3034</v>
       </c>
       <c r="V19" t="n">
         <v>1.2589</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2006</v>
+        <v>4.1668</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0285</v>
+        <v>-0.2485</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1721</v>
+        <v>4.4154</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7199</v>
+        <v>3.906</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2668</v>
+        <v>3.743</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4531</v>
+        <v>0.163</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5356</v>
+        <v>2.6748</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8199</v>
+        <v>2.5504</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7157</v>
+        <v>0.1244</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1843</v>
+        <v>1.2312</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4469</v>
+        <v>1.1926</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.0386</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5362</v>
+        <v>0.4461</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1604</v>
+        <v>-0.4405</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3758</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.3272</v>
+        <v>3.9389</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7382</v>
+        <v>1.7347</v>
       </c>
       <c r="F21" t="n">
-        <v>4.0654</v>
+        <v>2.2042</v>
       </c>
       <c r="G21" t="n">
-        <v>3.906</v>
+        <v>2.7199</v>
       </c>
       <c r="H21" t="n">
-        <v>3.743</v>
+        <v>1.2668</v>
       </c>
       <c r="I21" t="n">
-        <v>0.163</v>
+        <v>1.4531</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6748</v>
+        <v>1.5356</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5504</v>
+        <v>0.8199</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1244</v>
+        <v>0.7157</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2312</v>
+        <v>1.1843</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1926</v>
+        <v>0.4469</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0386</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3935</v>
+        <v>0.2745</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9302</v>
+        <v>-0.1334</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5367</v>
+        <v>0.4079</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.63</v>
+        <v>1.2589</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.8859</v>
+        <v>3.0068</v>
       </c>
       <c r="E22" t="n">
         <v>-1.2752</v>
       </c>
       <c r="F22" t="n">
-        <v>4.1611</v>
+        <v>4.2819</v>
       </c>
       <c r="G22" t="n">
         <v>1.8977</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>0.859</v>
+        <v>0.9799</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0584</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9175</v>
+        <v>1.0383</v>
       </c>
       <c r="V22" t="n">
         <v>0.3144</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. SAUCEDO GOMEZ URIBARRI</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0441</v>
+        <v>0.2461</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0.1666</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0441</v>
+        <v>0.4127</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4147</v>
+        <v>-1.7253</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.445</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4147</v>
+        <v>-3.1703</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.8589</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-1.8342</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4147</v>
+        <v>-0.75</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4147</v>
+        <v>-1.3361</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-0.4501</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.6068</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>G. SAUCEDO GOMEZ URIBARRI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4164</v>
+        <v>-0.0441</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1666</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2498</v>
+        <v>-0.0441</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7253</v>
+        <v>-0.4147</v>
       </c>
       <c r="H25" t="n">
-        <v>1.445</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.1703</v>
+        <v>-0.4147</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9752999999999999</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8589</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.8342</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.75</v>
+        <v>-0.4147</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5862000000000001</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.3361</v>
+        <v>-0.4147</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5059</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4501</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0557</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4812</v>
+        <v>-0.7504</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4048</v>
+        <v>0.111</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.886</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0205</v>
@@ -2560,13 +2560,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5387</v>
+        <v>0.2695</v>
       </c>
       <c r="T27" t="n">
-        <v>0.6529</v>
+        <v>0.3591</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6289</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.8389</v>
+        <v>-1.1924</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.8453</v>
+        <v>-4.0412</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0064</v>
+        <v>2.8488</v>
       </c>
       <c r="G28" t="n">
         <v>-0.5787</v>
@@ -2638,13 +2638,13 @@
         <v>2.2234</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2221</v>
+        <v>0.8686</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4726</v>
+        <v>0.2767</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.2505</v>
+        <v>0.5919</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>34.96469999999999</v>
+        <v>38.88180000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>12.3512</v>
+        <v>12.3511</v>
       </c>
       <c r="F29" t="n">
-        <v>22.6135</v>
+        <v>26.5307</v>
       </c>
       <c r="G29" t="n">
         <v>18.7926</v>
@@ -2704,7 +2704,7 @@
         <v>10.8089</v>
       </c>
       <c r="O29" t="n">
-        <v>-7.140599999999999</v>
+        <v>-7.1406</v>
       </c>
       <c r="P29" t="n">
         <v>3.7058</v>
@@ -2716,13 +2716,13 @@
         <v>17.6023</v>
       </c>
       <c r="S29" t="n">
-        <v>1.7656</v>
+        <v>5.682799999999999</v>
       </c>
       <c r="T29" t="n">
         <v>-0.205</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9708</v>
+        <v>5.887999999999999</v>
       </c>
       <c r="V29" t="n">
         <v>10.7003</v>
